--- a/public/WOA_DMR_Monthly_Report.xlsx
+++ b/public/WOA_DMR_Monthly_Report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC68EA8A-2197-407E-A147-68B2D668DBA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCC3EE7-6F03-4995-8620-73ED55587D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,7 +222,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,20 +290,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF000000"/>
@@ -935,7 +921,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -950,98 +936,134 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="46" fontId="10" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="15" fontId="10" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="9" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="9" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="46" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="46" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1196,149 +1218,41 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="46" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1783,1087 +1697,1025 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="42"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="A1" s="54"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
     </row>
     <row r="2" spans="1:18" ht="100.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="46" t="s">
+      <c r="A2" s="55"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="51"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="63"/>
     </row>
     <row r="3" spans="1:18" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
     </row>
     <row r="4" spans="1:18" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="55"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="67"/>
     </row>
     <row r="5" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="76" t="s">
+      <c r="B5" s="85"/>
+      <c r="C5" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="77"/>
-      <c r="E5" s="80" t="s">
+      <c r="D5" s="89"/>
+      <c r="E5" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="76" t="s">
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="86" t="s">
+      <c r="K5" s="96"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="96"/>
+      <c r="O5" s="96"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="R5" s="40"/>
+      <c r="R5" s="52"/>
     </row>
     <row r="6" spans="1:18" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="74"/>
-      <c r="B6" s="75"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="85"/>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="85"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="87"/>
-      <c r="R6" s="41"/>
+      <c r="A6" s="86"/>
+      <c r="B6" s="87"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="97"/>
+      <c r="O6" s="97"/>
+      <c r="P6" s="91"/>
+      <c r="Q6" s="99"/>
+      <c r="R6" s="53"/>
     </row>
     <row r="7" spans="1:18" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="59"/>
+      <c r="A7" s="71"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
     </row>
     <row r="8" spans="1:18" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
-      <c r="N8" s="61"/>
-      <c r="O8" s="61"/>
-      <c r="P8" s="61"/>
-      <c r="Q8" s="61"/>
-      <c r="R8" s="62"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="73"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="73"/>
+      <c r="R8" s="74"/>
     </row>
     <row r="9" spans="1:18" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="65" t="s">
+      <c r="C9" s="76"/>
+      <c r="D9" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="68" t="s">
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="68" t="s">
+      <c r="K9" s="81"/>
+      <c r="L9" s="81"/>
+      <c r="M9" s="81"/>
+      <c r="N9" s="81"/>
+      <c r="O9" s="82"/>
+      <c r="P9" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" s="69"/>
-      <c r="R9" s="71"/>
+      <c r="Q9" s="81"/>
+      <c r="R9" s="83"/>
     </row>
     <row r="10" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>1</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="57" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-      <c r="N10" s="57"/>
-      <c r="O10" s="57"/>
-      <c r="P10" s="57"/>
-      <c r="Q10" s="57"/>
-      <c r="R10" s="58"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="69"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="69"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="69"/>
+      <c r="Q10" s="69"/>
+      <c r="R10" s="70"/>
     </row>
     <row r="11" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>2</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="39"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="50"/>
+      <c r="L11" s="50"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="50"/>
+      <c r="O11" s="50"/>
+      <c r="P11" s="50"/>
+      <c r="Q11" s="50"/>
+      <c r="R11" s="51"/>
     </row>
     <row r="12" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>3</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="39"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="51"/>
     </row>
     <row r="13" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>4</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="39"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="51"/>
     </row>
     <row r="14" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>5</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="38"/>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="39"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="50"/>
+      <c r="L14" s="50"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="51"/>
     </row>
     <row r="15" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>6</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="38"/>
-      <c r="R15" s="39"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="50"/>
+      <c r="L15" s="50"/>
+      <c r="M15" s="50"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="50"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="50"/>
+      <c r="R15" s="51"/>
     </row>
     <row r="16" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>7</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="39"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K16" s="50"/>
+      <c r="L16" s="50"/>
+      <c r="M16" s="50"/>
+      <c r="N16" s="50"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="51"/>
     </row>
     <row r="17" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>8</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="38"/>
-      <c r="R17" s="39"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="50"/>
+      <c r="L17" s="50"/>
+      <c r="M17" s="50"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="50"/>
+      <c r="P17" s="50"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="51"/>
     </row>
     <row r="18" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>8</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="38"/>
-      <c r="R18" s="39"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K18" s="50"/>
+      <c r="L18" s="50"/>
+      <c r="M18" s="50"/>
+      <c r="N18" s="50"/>
+      <c r="O18" s="50"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="50"/>
+      <c r="R18" s="51"/>
     </row>
     <row r="19" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>9</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="38"/>
-      <c r="R19" s="39"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="50"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="50"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="50"/>
+      <c r="Q19" s="50"/>
+      <c r="R19" s="51"/>
     </row>
     <row r="20" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>10</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-      <c r="R20" s="39"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
+      <c r="M20" s="50"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="51"/>
     </row>
     <row r="21" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>11</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38" t="s">
+      <c r="C21" s="49"/>
+      <c r="D21" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38" t="s">
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38" t="s">
+      <c r="K21" s="50"/>
+      <c r="L21" s="50"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="39"/>
+      <c r="Q21" s="50"/>
+      <c r="R21" s="51"/>
     </row>
     <row r="22" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>12</v>
       </c>
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="38"/>
-      <c r="R22" s="39"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22" s="50"/>
+      <c r="L22" s="50"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="50"/>
+      <c r="P22" s="50"/>
+      <c r="Q22" s="50"/>
+      <c r="R22" s="51"/>
     </row>
     <row r="23" spans="1:18" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>13</v>
       </c>
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="39"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K23" s="50"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="50"/>
+      <c r="Q23" s="50"/>
+      <c r="R23" s="51"/>
     </row>
     <row r="24" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>14</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="38"/>
-      <c r="Q24" s="38"/>
-      <c r="R24" s="39"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="50"/>
+      <c r="P24" s="50"/>
+      <c r="Q24" s="50"/>
+      <c r="R24" s="51"/>
     </row>
     <row r="25" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>15</v>
       </c>
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-      <c r="R25" s="39"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K25" s="50"/>
+      <c r="L25" s="50"/>
+      <c r="M25" s="50"/>
+      <c r="N25" s="50"/>
+      <c r="O25" s="50"/>
+      <c r="P25" s="50"/>
+      <c r="Q25" s="50"/>
+      <c r="R25" s="51"/>
     </row>
     <row r="26" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>16</v>
       </c>
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="38"/>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="39"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K26" s="50"/>
+      <c r="L26" s="50"/>
+      <c r="M26" s="50"/>
+      <c r="N26" s="50"/>
+      <c r="O26" s="50"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="51"/>
     </row>
     <row r="27" spans="1:18" ht="80.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>17</v>
       </c>
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="88"/>
-      <c r="D27" s="89" t="s">
+      <c r="C27" s="39"/>
+      <c r="D27" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="89"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="89"/>
-      <c r="H27" s="89"/>
-      <c r="I27" s="89"/>
-      <c r="J27" s="89" t="s">
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K27" s="89"/>
-      <c r="L27" s="89"/>
-      <c r="M27" s="89"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="89"/>
-      <c r="P27" s="90"/>
-      <c r="Q27" s="90"/>
-      <c r="R27" s="91"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="40"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="1:18" s="5" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="92"/>
-      <c r="B28" s="93"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="93"/>
-      <c r="E28" s="93"/>
-      <c r="F28" s="93"/>
-      <c r="G28" s="93"/>
-      <c r="H28" s="93"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="93"/>
-      <c r="M28" s="93"/>
-      <c r="N28" s="93"/>
-      <c r="O28" s="93"/>
-      <c r="P28" s="93"/>
-      <c r="Q28" s="93"/>
-      <c r="R28" s="94"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="44"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="45"/>
     </row>
     <row r="29" spans="1:18" s="5" customFormat="1" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="95" t="s">
+      <c r="A29" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="96"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="96"/>
-      <c r="E29" s="96"/>
-      <c r="F29" s="96"/>
-      <c r="G29" s="96"/>
-      <c r="H29" s="96"/>
-      <c r="I29" s="96"/>
-      <c r="J29" s="96"/>
-      <c r="K29" s="96"/>
-      <c r="L29" s="96"/>
-      <c r="M29" s="96"/>
-      <c r="N29" s="96"/>
-      <c r="O29" s="96"/>
-      <c r="P29" s="96"/>
-      <c r="Q29" s="96"/>
-      <c r="R29" s="97"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="47"/>
+      <c r="N29" s="47"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="47"/>
+      <c r="Q29" s="47"/>
+      <c r="R29" s="48"/>
     </row>
     <row r="30" spans="1:18" s="5" customFormat="1" ht="67.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="103" t="s">
+      <c r="A30" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="105" t="s">
+      <c r="B30" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="107" t="s">
+      <c r="C30" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="108"/>
-      <c r="E30" s="107" t="s">
+      <c r="D30" s="34"/>
+      <c r="E30" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="100" t="s">
+      <c r="F30" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="G30" s="111" t="s">
+      <c r="G30" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="H30" s="112"/>
-      <c r="I30" s="111" t="s">
+      <c r="H30" s="38"/>
+      <c r="I30" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="J30" s="112"/>
-      <c r="K30" s="111" t="s">
+      <c r="J30" s="38"/>
+      <c r="K30" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="L30" s="112"/>
-      <c r="M30" s="101" t="s">
+      <c r="L30" s="38"/>
+      <c r="M30" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="N30" s="101" t="s">
+      <c r="N30" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="O30" s="101" t="s">
+      <c r="O30" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="P30" s="101" t="s">
+      <c r="P30" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="Q30" s="100" t="s">
+      <c r="Q30" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="R30" s="101" t="s">
+      <c r="R30" s="27" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="5" customFormat="1" ht="67.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="104"/>
-      <c r="B31" s="106"/>
-      <c r="C31" s="109"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="101"/>
-      <c r="G31" s="10" t="s">
+    <row r="31" spans="1:18" s="5" customFormat="1" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="30"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="K31" s="10" t="s">
+      <c r="K31" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="L31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M31" s="102"/>
-      <c r="N31" s="102"/>
-      <c r="O31" s="102"/>
-      <c r="P31" s="102"/>
-      <c r="Q31" s="101"/>
-      <c r="R31" s="102"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="28"/>
     </row>
     <row r="32" spans="1:18" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="16"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="99"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="21"/>
-      <c r="R32" s="34"/>
+      <c r="A32" s="100"/>
+      <c r="B32" s="101"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="106"/>
+      <c r="H32" s="107"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="108"/>
+      <c r="K32" s="108"/>
+      <c r="L32" s="108"/>
+      <c r="M32" s="109"/>
+      <c r="N32" s="110"/>
+      <c r="O32" s="109"/>
+      <c r="P32" s="110"/>
+      <c r="Q32" s="105"/>
+      <c r="R32" s="111"/>
     </row>
     <row r="33" spans="1:18" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="120"/>
-      <c r="D33" s="121"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="35"/>
-    </row>
-    <row r="34" spans="1:18" ht="77.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="25"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="134"/>
-      <c r="D34" s="135"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="33"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="36"/>
+      <c r="A33" s="100"/>
+      <c r="B33" s="101"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="106"/>
+      <c r="H33" s="107"/>
+      <c r="I33" s="101"/>
+      <c r="J33" s="108"/>
+      <c r="K33" s="108"/>
+      <c r="L33" s="108"/>
+      <c r="M33" s="109"/>
+      <c r="N33" s="110"/>
+      <c r="O33" s="109"/>
+      <c r="P33" s="110"/>
+      <c r="Q33" s="105"/>
+      <c r="R33" s="111"/>
+    </row>
+    <row r="34" spans="1:18" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="100"/>
+      <c r="B34" s="101"/>
+      <c r="C34" s="102"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="107"/>
+      <c r="I34" s="101"/>
+      <c r="J34" s="108"/>
+      <c r="K34" s="108"/>
+      <c r="L34" s="108"/>
+      <c r="M34" s="109"/>
+      <c r="N34" s="110"/>
+      <c r="O34" s="109"/>
+      <c r="P34" s="110"/>
+      <c r="Q34" s="105"/>
+      <c r="R34" s="111"/>
     </row>
     <row r="35" spans="1:18" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="114"/>
-      <c r="C35" s="114"/>
-      <c r="D35" s="114"/>
-      <c r="E35" s="114"/>
-      <c r="F35" s="114"/>
-      <c r="G35" s="114"/>
-      <c r="H35" s="114"/>
-      <c r="I35" s="114"/>
-      <c r="J35" s="114"/>
-      <c r="K35" s="114"/>
-      <c r="L35" s="114"/>
-      <c r="M35" s="114"/>
-      <c r="N35" s="114"/>
-      <c r="O35" s="114"/>
-      <c r="P35" s="114"/>
-      <c r="Q35" s="114"/>
-      <c r="R35" s="115"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="9"/>
     </row>
     <row r="36" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="116" t="s">
+      <c r="A36" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="117"/>
-      <c r="C36" s="117"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="117"/>
-      <c r="F36" s="117"/>
-      <c r="G36" s="118" t="s">
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H36" s="118"/>
-      <c r="I36" s="118"/>
-      <c r="J36" s="118"/>
-      <c r="K36" s="118"/>
-      <c r="L36" s="118"/>
-      <c r="M36" s="118"/>
-      <c r="N36" s="118"/>
-      <c r="O36" s="118"/>
-      <c r="P36" s="118"/>
-      <c r="Q36" s="118"/>
-      <c r="R36" s="119"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="12"/>
+      <c r="P36" s="12"/>
+      <c r="Q36" s="12"/>
+      <c r="R36" s="13"/>
     </row>
     <row r="37" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="129" t="s">
+      <c r="A37" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="130"/>
-      <c r="C37" s="130"/>
-      <c r="D37" s="130" t="s">
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E37" s="130"/>
-      <c r="F37" s="130"/>
-      <c r="G37" s="130" t="s">
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="H37" s="130"/>
-      <c r="I37" s="130"/>
-      <c r="J37" s="130" t="s">
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="K37" s="130"/>
-      <c r="L37" s="130"/>
-      <c r="M37" s="130"/>
-      <c r="N37" s="131" t="s">
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="O37" s="132"/>
-      <c r="P37" s="132"/>
-      <c r="Q37" s="130" t="s">
+      <c r="O37" s="24"/>
+      <c r="P37" s="24"/>
+      <c r="Q37" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="R37" s="133"/>
+      <c r="R37" s="25"/>
     </row>
     <row r="38" spans="1:18" ht="183.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="122" t="s">
+      <c r="A38" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="123"/>
-      <c r="C38" s="124"/>
-      <c r="D38" s="125"/>
-      <c r="E38" s="125"/>
-      <c r="F38" s="125"/>
-      <c r="G38" s="126" t="s">
+      <c r="B38" s="15"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="H38" s="126"/>
-      <c r="I38" s="126"/>
-      <c r="J38" s="126"/>
-      <c r="K38" s="126"/>
-      <c r="L38" s="126"/>
-      <c r="M38" s="126"/>
-      <c r="N38" s="127" t="s">
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="O38" s="123"/>
-      <c r="P38" s="123"/>
-      <c r="Q38" s="126"/>
-      <c r="R38" s="128"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="124">
-    <mergeCell ref="A35:R35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="G36:R36"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="R30:R31"/>
-    <mergeCell ref="N30:N31"/>
-    <mergeCell ref="O30:O31"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="J27:O27"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="A28:R28"/>
-    <mergeCell ref="A29:R29"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="J25:O25"/>
-    <mergeCell ref="P25:R25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="J26:O26"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:I23"/>
-    <mergeCell ref="J23:O23"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="J24:O24"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:I21"/>
-    <mergeCell ref="J21:O21"/>
-    <mergeCell ref="P21:R21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="J22:O22"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="J19:O19"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="J20:O20"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="J16:O16"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="J17:O17"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="J18:O18"/>
-    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="J11:O11"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="J14:O14"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="J15:O15"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="J12:O12"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="J13:O13"/>
+    <mergeCell ref="P13:R13"/>
     <mergeCell ref="R5:R6"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:C2"/>
@@ -2886,26 +2738,88 @@
     <mergeCell ref="E5:I6"/>
     <mergeCell ref="J5:P6"/>
     <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="J11:O11"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="J14:O14"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="J15:O15"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="J12:O12"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="J13:O13"/>
-    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="J19:O19"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="J20:O20"/>
+    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="J16:O16"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="J17:O17"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="J18:O18"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="J23:O23"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="J24:O24"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="J21:O21"/>
+    <mergeCell ref="P21:R21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="J27:O27"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="A28:R28"/>
+    <mergeCell ref="A29:R29"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="J25:O25"/>
+    <mergeCell ref="P25:R25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="J26:O26"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="R30:R31"/>
+    <mergeCell ref="N30:N31"/>
+    <mergeCell ref="O30:O31"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="A35:R35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="G36:R36"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="C34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
